--- a/.yuleosh/reports/layer3-report.xlsx
+++ b/.yuleosh/reports/layer3-report.xlsx
@@ -504,13 +504,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
     </row>
@@ -569,14 +569,10 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>No E2E tests</t>
-        </is>
-      </c>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">

--- a/.yuleosh/reports/layer3-report.xlsx
+++ b/.yuleosh/reports/layer3-report.xlsx
@@ -500,14 +500,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
@@ -569,10 +569,18 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr"/>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>.F
+=================================== FAILURES ===================================
+________________________________ test_crc_real _________________________________
+    def test_func():
+        build</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">

--- a/.yuleosh/reports/layer3-report.xlsx
+++ b/.yuleosh/reports/layer3-report.xlsx
@@ -500,14 +500,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>failed</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
@@ -569,18 +569,10 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>.F
-=================================== FAILURES ===================================
-________________________________ test_crc_real _________________________________
-    def test_func():
-        build</t>
-        </is>
-      </c>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">

--- a/.yuleosh/reports/layer3-report.xlsx
+++ b/.yuleosh/reports/layer3-report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stages" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stages" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,14 +500,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
@@ -569,10 +569,17 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr"/>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>....F
+=================================== FAILURES ===================================
+________________________ test_ci_layer23_no_misra_check ________________________
+    def test_ci_layer23_no_misr</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
